--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008402251151435237</v>
       </c>
       <c r="C2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>9880721</v>
+        <v>4836882</v>
       </c>
       <c r="L2" t="n">
-        <v>6255664</v>
+        <v>2991338</v>
       </c>
       <c r="M2" t="n">
-        <v>1712825</v>
+        <v>783023</v>
       </c>
       <c r="N2" t="n">
-        <v>123760</v>
+        <v>45293</v>
       </c>
       <c r="O2" t="n">
-        <v>967899</v>
+        <v>459103</v>
       </c>
       <c r="P2" t="n">
-        <v>372453</v>
+        <v>179702</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999963641166687</v>
+        <v>0.9999962449073792</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9774565100669861</v>
+        <v>0.9562498331069946</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9419292807579041</v>
+        <v>0.894680380821228</v>
       </c>
       <c r="T2" t="n">
-        <v>0.929912805557251</v>
+        <v>0.8682706952095032</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8693208694458008</v>
+        <v>0.7105675935745239</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9495871663093567</v>
+        <v>0.9009244441986084</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9656772017478943</v>
+        <v>0.9320884943008423</v>
       </c>
       <c r="X2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>9714356</v>
+        <v>4854570</v>
       </c>
       <c r="AG2" t="n">
-        <v>5956664</v>
+        <v>2980268</v>
       </c>
       <c r="AH2" t="n">
-        <v>1601221</v>
+        <v>800821</v>
       </c>
       <c r="AI2" t="n">
-        <v>118175</v>
+        <v>59096</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917973</v>
+        <v>459081</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567423462867737</v>
+        <v>0.9567334651947021</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911146342754364</v>
+        <v>0.9111363887786865</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582749962806702</v>
+        <v>0.8581864833831787</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627725958824158</v>
+        <v>0.6625929474830627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020447134971619</v>
+        <v>0.9019822478294373</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -795,13 +795,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9880721</v>
+        <v>4836882</v>
       </c>
       <c r="E3" t="n">
-        <v>259676</v>
+        <v>229421</v>
       </c>
       <c r="F3" t="n">
-        <v>2369</v>
+        <v>2354</v>
       </c>
       <c r="G3" t="n">
         <v>560</v>
@@ -813,109 +813,109 @@
         <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>20139194</v>
+        <v>10069596</v>
       </c>
       <c r="K3" t="n">
-        <v>22460701</v>
+        <v>11125397</v>
       </c>
       <c r="L3" t="n">
-        <v>25900535</v>
+        <v>12789004</v>
       </c>
       <c r="M3" t="n">
-        <v>30836040</v>
+        <v>15363494</v>
       </c>
       <c r="N3" t="n">
-        <v>32634942</v>
+        <v>16308286</v>
       </c>
       <c r="O3" t="n">
-        <v>31762453</v>
+        <v>15856319</v>
       </c>
       <c r="P3" t="n">
-        <v>32432217</v>
+        <v>16209625</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9741019010543823</v>
+        <v>0.9541505575180054</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9556763172149658</v>
+        <v>0.9134238362312317</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9174873232841492</v>
+        <v>0.8386147618293762</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6935120820999146</v>
+        <v>0.507399320602417</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9506335854530334</v>
+        <v>0.9016286730766296</v>
       </c>
       <c r="W3" t="n">
-        <v>0.963543713092804</v>
+        <v>0.9297399520874023</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9714356</v>
+        <v>4854570</v>
       </c>
       <c r="Z3" t="n">
-        <v>398208</v>
+        <v>199283</v>
       </c>
       <c r="AA3" t="n">
-        <v>17110</v>
+        <v>8572</v>
       </c>
       <c r="AB3" t="n">
-        <v>13592</v>
+        <v>6807</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20139240</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>22249364</v>
+        <v>11127154</v>
       </c>
       <c r="AG3" t="n">
-        <v>25705317</v>
+        <v>12850470</v>
       </c>
       <c r="AH3" t="n">
-        <v>30700729</v>
+        <v>15349956</v>
       </c>
       <c r="AI3" t="n">
-        <v>32593417</v>
+        <v>16296642</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31714153</v>
+        <v>15856919</v>
       </c>
       <c r="AK3" t="n">
-        <v>32418947</v>
+        <v>16209464</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9577006697654724</v>
+        <v>0.957639753818512</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099981188774109</v>
+        <v>0.9100435376167297</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85770583152771</v>
+        <v>0.8576763868331909</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6622154712677002</v>
+        <v>0.6620287895202637</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015981554985046</v>
+        <v>0.9015854597091675</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,13 +929,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>213359</v>
+        <v>206855</v>
       </c>
       <c r="E4" t="n">
-        <v>6255664</v>
+        <v>2991338</v>
       </c>
       <c r="F4" t="n">
-        <v>74361</v>
+        <v>74256</v>
       </c>
       <c r="G4" t="n">
         <v>1203</v>
@@ -947,109 +947,109 @@
         <v>53</v>
       </c>
       <c r="J4" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>227883</v>
+        <v>221296</v>
       </c>
       <c r="L4" t="n">
-        <v>385667</v>
+        <v>352133</v>
       </c>
       <c r="M4" t="n">
-        <v>129095</v>
+        <v>118796</v>
       </c>
       <c r="N4" t="n">
-        <v>18604</v>
+        <v>18449</v>
       </c>
       <c r="O4" t="n">
-        <v>51385</v>
+        <v>50488</v>
       </c>
       <c r="P4" t="n">
-        <v>13238</v>
+        <v>13093</v>
       </c>
       <c r="Q4" t="n">
         <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9757763743400574</v>
+        <v>0.9551990628242493</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9487529993057251</v>
+        <v>0.9039549231529236</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9236582517623901</v>
+        <v>0.8531851172447205</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7715277671813965</v>
+        <v>0.5920382738113403</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9501100778579712</v>
+        <v>0.9012764096260071</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9646092653274536</v>
+        <v>0.9309127330780029</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>410116</v>
+        <v>204986</v>
       </c>
       <c r="Z4" t="n">
-        <v>5956664</v>
+        <v>2980268</v>
       </c>
       <c r="AA4" t="n">
-        <v>165604</v>
+        <v>82895</v>
       </c>
       <c r="AB4" t="n">
-        <v>10994</v>
+        <v>5498</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>439220</v>
+        <v>219539</v>
       </c>
       <c r="AG4" t="n">
-        <v>580885</v>
+        <v>290667</v>
       </c>
       <c r="AH4" t="n">
-        <v>264406</v>
+        <v>132334</v>
       </c>
       <c r="AI4" t="n">
-        <v>60129</v>
+        <v>30093</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99685</v>
+        <v>49888</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572212696075439</v>
+        <v>0.9571864008903503</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9105718731880188</v>
+        <v>0.9105896949768066</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579903244972229</v>
+        <v>0.8579313158988953</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.662493884563446</v>
+        <v>0.662310779094696</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018213748931885</v>
+        <v>0.90178382396698</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,19 +1059,19 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>8224</v>
+        <v>8151</v>
       </c>
       <c r="E5" t="n">
-        <v>107106</v>
+        <v>103922</v>
       </c>
       <c r="F5" t="n">
-        <v>1712825</v>
+        <v>783023</v>
       </c>
       <c r="G5" t="n">
-        <v>8932</v>
+        <v>8837</v>
       </c>
       <c r="H5" t="n">
-        <v>29176</v>
+        <v>29175</v>
       </c>
       <c r="I5" t="n">
         <v>601</v>
@@ -1080,106 +1080,106 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>262695</v>
+        <v>232425</v>
       </c>
       <c r="L5" t="n">
-        <v>290134</v>
+        <v>283525</v>
       </c>
       <c r="M5" t="n">
-        <v>154040</v>
+        <v>150687</v>
       </c>
       <c r="N5" t="n">
-        <v>54694</v>
+        <v>43972</v>
       </c>
       <c r="O5" t="n">
-        <v>50263</v>
+        <v>50090</v>
       </c>
       <c r="P5" t="n">
-        <v>14092</v>
+        <v>13580</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999985694885254</v>
+        <v>0.9999985098838806</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9850579500198364</v>
+        <v>0.9723610281944275</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9794163703918457</v>
+        <v>0.9612781405448914</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9913762211799622</v>
+        <v>0.9835841059684753</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9977675080299377</v>
+        <v>0.996197521686554</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9969040155410767</v>
+        <v>0.9938731789588928</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9991675615310669</v>
+        <v>0.9983751773834229</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>16069</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>170194</v>
+        <v>85136</v>
       </c>
       <c r="AA5" t="n">
-        <v>1601221</v>
+        <v>800821</v>
       </c>
       <c r="AB5" t="n">
-        <v>19877</v>
+        <v>9950</v>
       </c>
       <c r="AC5" t="n">
-        <v>58238</v>
+        <v>29139</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>429060</v>
+        <v>214737</v>
       </c>
       <c r="AG5" t="n">
-        <v>589134</v>
+        <v>294595</v>
       </c>
       <c r="AH5" t="n">
-        <v>265644</v>
+        <v>132889</v>
       </c>
       <c r="AI5" t="n">
-        <v>60279</v>
+        <v>30169</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100189</v>
+        <v>50112</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735538363456726</v>
+        <v>0.9735455513000488</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643634557723999</v>
+        <v>0.9643480777740479</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983855664730072</v>
+        <v>0.9838436245918274</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996332585811615</v>
+        <v>0.9963290691375732</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939122200012207</v>
+        <v>0.9939084053039551</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983846545219421</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
@@ -1189,22 +1189,22 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6259</v>
+        <v>6249</v>
       </c>
       <c r="E6" t="n">
-        <v>17975</v>
+        <v>17880</v>
       </c>
       <c r="F6" t="n">
-        <v>22373</v>
+        <v>12194</v>
       </c>
       <c r="G6" t="n">
-        <v>123760</v>
+        <v>45293</v>
       </c>
       <c r="H6" t="n">
-        <v>7622</v>
+        <v>7209</v>
       </c>
       <c r="I6" t="n">
-        <v>459</v>
+        <v>434</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12924</v>
+        <v>6466</v>
       </c>
       <c r="Z6" t="n">
-        <v>10697</v>
+        <v>5355</v>
       </c>
       <c r="AA6" t="n">
-        <v>21742</v>
+        <v>10880</v>
       </c>
       <c r="AB6" t="n">
-        <v>118175</v>
+        <v>59096</v>
       </c>
       <c r="AC6" t="n">
-        <v>13954</v>
+        <v>6987</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>23</v>
@@ -1272,13 +1272,13 @@
         <v>29666</v>
       </c>
       <c r="G7" t="n">
-        <v>7651</v>
+        <v>7599</v>
       </c>
       <c r="H7" t="n">
-        <v>967899</v>
+        <v>459103</v>
       </c>
       <c r="I7" t="n">
-        <v>12107</v>
+        <v>11987</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1624</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>59290</v>
+        <v>29657</v>
       </c>
       <c r="AB7" t="n">
-        <v>15136</v>
+        <v>7573</v>
       </c>
       <c r="AC7" t="n">
-        <v>917973</v>
+        <v>459081</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
         <v>18</v>
@@ -1346,13 +1346,13 @@
         <v>326</v>
       </c>
       <c r="G8" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="H8" t="n">
-        <v>13357</v>
+        <v>12874</v>
       </c>
       <c r="I8" t="n">
-        <v>372453</v>
+        <v>179702</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
